--- a/Projects from Mars Electric/Inventory Optimization Project - VMI Specialist.xlsx
+++ b/Projects from Mars Electric/Inventory Optimization Project - VMI Specialist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c2c94\OneDrive\Desktop\Careers\Waddle Portfolio\data-portfolio\Projects from Mars Electric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7AF25E-F6B7-45B7-B71F-FAB3E8CCD0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC3D09D-B3CD-49B0-8B6D-6088379E2EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Optimized Data" sheetId="4" r:id="rId1"/>
@@ -347,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
@@ -408,8 +408,15 @@
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +453,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,14 +555,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -569,15 +582,48 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="5" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="Bad" xfId="5" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="4" builtinId="10"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -665,13 +711,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>12699</xdr:rowOff>
+      <xdr:rowOff>12698</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -686,8 +732,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14192250" y="4718049"/>
-          <a:ext cx="5010150" cy="2892426"/>
+          <a:off x="14001750" y="4965698"/>
+          <a:ext cx="4800600" cy="3397251"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -742,22 +788,22 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US"/>
-            <a:t>While the original estimates proved directionally accurate, my analysis validated their logic and shifted the conversation—prompting the client to investigate internal causes for stockouts rather than placing blame externally. This not only built trust but also improved collaboration.</a:t>
+            <a:t>While the original estimates proved directionally accurate, my analysis validated their logic and shifted the conversation,</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US"/>
+          <a:r>
+            <a:rPr lang="en-US" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>prompting the client to investigate internal causes for stockouts rather than placing blame externally. As part of this process, I also flagged products averaging fewer than 20 units per month (or fewer than 5 per week) for phase-out from customer inventory, reducing unnecessary SKU complexity and improving overall stock discipline. This not only built trust but also improved collaboration.</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US"/>
-            <a:t>By implementing “optimized weekly” columns to define new inventory maxes,</a:t>
+            <a:t>By implementing “optimized weekly” columns to define new inventory maxes, it instantly cut same-day deliveries by half, saving $1,500+. With full implementation, this new layout could save close to $10,000 annually. All in all, this new blueprint satisfies the needs of the customer and Mars without compromise.</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" baseline="0"/>
-            <a:t> it instantly cut same-day deliveries by half, saving $1,500 +. With a full implementation, this new layout could save close to $10,000 annually. All in all, this new blueprint satifisfies the needs of the customer and Mars without compromise.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1166,23 +1212,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F24B7BB-3E39-4FE8-B616-C239858AE6AC}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.81640625" customWidth="1"/>
+    <col min="1" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" customWidth="1"/>
-    <col min="9" max="9" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="15.1796875" customWidth="1"/>
-    <col min="13" max="13" width="30.1796875" customWidth="1"/>
-    <col min="14" max="14" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="30.140625" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
@@ -1226,7 +1272,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>50</v>
       </c>
@@ -1285,7 +1331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>50</v>
       </c>
@@ -1305,7 +1351,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A3," ",'Optimized Data'!$B3)</f>
         <v>3M TAPE</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="7">
@@ -1344,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>50</v>
       </c>
@@ -1356,7 +1402,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A4," ",'Optimized Data'!$B4)</f>
         <v>3M TAPE</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="18" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4">
@@ -1395,7 +1441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>50</v>
       </c>
@@ -1407,7 +1453,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A5," ",'Optimized Data'!$B5)</f>
         <v>3M TAPE</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="7">
@@ -1446,7 +1492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -1497,7 +1543,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>50</v>
       </c>
@@ -1509,7 +1555,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A7," ",'Optimized Data'!$B7)</f>
         <v>3M STACKER</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="7">
@@ -1548,7 +1594,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>50</v>
       </c>
@@ -1599,7 +1645,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>48</v>
       </c>
@@ -1611,7 +1657,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A9," ",'Optimized Data'!$B9)</f>
         <v>AMFI CONN</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="7">
@@ -1650,7 +1696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>48</v>
       </c>
@@ -1662,7 +1708,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A10," ",'Optimized Data'!$B10)</f>
         <v>AMFI BUSHING</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="4">
@@ -1701,7 +1747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>48</v>
       </c>
@@ -1713,7 +1759,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A11," ",'Optimized Data'!$B11)</f>
         <v>AMFI CONN</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="7">
@@ -1752,7 +1798,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>48</v>
       </c>
@@ -1803,7 +1849,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>48</v>
       </c>
@@ -1854,7 +1900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>52</v>
       </c>
@@ -1905,7 +1951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>54</v>
       </c>
@@ -1956,7 +2002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>54</v>
       </c>
@@ -1968,7 +2014,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A16," ",'Optimized Data'!$B16)</f>
         <v>ARL TERMINATOR</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="18" t="s">
         <v>36</v>
       </c>
       <c r="E16" s="4">
@@ -2007,7 +2053,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>54</v>
       </c>
@@ -2019,7 +2065,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A17," ",'Optimized Data'!$B17)</f>
         <v>ARL TERMINATOR</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="7">
@@ -2058,7 +2104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>54</v>
       </c>
@@ -2109,7 +2155,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>54</v>
       </c>
@@ -2121,7 +2167,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A19," ",'Optimized Data'!$B19)</f>
         <v>ARL HANGER</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="7">
@@ -2160,7 +2206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>54</v>
       </c>
@@ -2211,7 +2257,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>54</v>
       </c>
@@ -2262,7 +2308,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>92</v>
       </c>
@@ -2274,7 +2320,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A22," ",'Optimized Data'!$B22)</f>
         <v>BRDGPORT CONDUIT</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="4">
@@ -2313,7 +2359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>92</v>
       </c>
@@ -2325,7 +2371,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A23," ",'Optimized Data'!$B23)</f>
         <v>BRDGPORT CONDUIT</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="7">
@@ -2364,7 +2410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>92</v>
       </c>
@@ -2376,7 +2422,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A24," ",'Optimized Data'!$B24)</f>
         <v>BRDGPORT COND</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="4">
@@ -2415,7 +2461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>92</v>
       </c>
@@ -2427,7 +2473,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A25," ",'Optimized Data'!$B25)</f>
         <v>BRDGPORT INSBSH</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="18" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="7">
@@ -2466,7 +2512,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>92</v>
       </c>
@@ -2508,7 +2554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>92</v>
       </c>
@@ -2520,7 +2566,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A27," ",'Optimized Data'!$B27)</f>
         <v>BRDGPORT INSBSH</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="7">
@@ -2550,7 +2596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>92</v>
       </c>
@@ -2592,7 +2638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>92</v>
       </c>
@@ -2634,7 +2680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>92</v>
       </c>
@@ -2676,7 +2722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>92</v>
       </c>
@@ -2688,7 +2734,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A31," ",'Optimized Data'!$B31)</f>
         <v>BRDGPORT FLEX</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="18" t="s">
         <v>37</v>
       </c>
       <c r="E31" s="7">
@@ -2718,7 +2764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>92</v>
       </c>
@@ -2760,7 +2806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>92</v>
       </c>
@@ -2802,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>92</v>
       </c>
@@ -2814,7 +2860,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A34," ",'Optimized Data'!$B34)</f>
         <v>BRDGPORT COND</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="18" t="s">
         <v>32</v>
       </c>
       <c r="E34" s="4">
@@ -2844,7 +2890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>92</v>
       </c>
@@ -2886,7 +2932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>92</v>
       </c>
@@ -2928,7 +2974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>92</v>
       </c>
@@ -2970,7 +3016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>92</v>
       </c>
@@ -2982,7 +3028,7 @@
         <f>_xlfn.CONCAT('Optimized Data'!$A38," ",'Optimized Data'!$B38)</f>
         <v>BRDGPORT EMT</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="18" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="4">
@@ -3012,7 +3058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>56</v>
       </c>
@@ -3054,7 +3100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>56</v>
       </c>
@@ -3098,6 +3144,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="H2:H40">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F39">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>20</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
